--- a/ZonasEscolares/excels/LA_LIBERTAD-SANCHEZ_CARRION-HUAMACHUCO.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-SANCHEZ_CARRION-HUAMACHUCO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -498,12 +498,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -550,12 +550,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -602,12 +602,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -706,12 +706,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -810,12 +810,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1694,12 +1694,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1746,12 +1746,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1798,12 +1798,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1902,12 +1902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1954,12 +1954,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2058,12 +2058,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2162,12 +2162,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2370,12 +2370,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2422,12 +2422,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SANCHEZ_CARRION</t>
+          <t>SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LA_LIBERTAD-SANCHEZ_CARRION-HUAMACHUCO.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-SANCHEZ_CARRION-HUAMACHUCO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>100</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-7.8123</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-78.0453</v>
-      </c>
-      <c r="I2" t="n">
-        <v>617</v>
-      </c>
-      <c r="J2" t="n">
-        <v>21</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-7.8123</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-78.0453</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>1718</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-7.8188</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-78.0397</v>
-      </c>
-      <c r="I3" t="n">
-        <v>267</v>
-      </c>
-      <c r="J3" t="n">
-        <v>11</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-7.8188</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-78.0397</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>1727</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-7.819586</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-78.043915</v>
-      </c>
-      <c r="I4" t="n">
-        <v>225</v>
-      </c>
-      <c r="J4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-7.819586</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-78.043915</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>CUNA JARDIN HUAMACHUCO</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-7.8154</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-78.0467</v>
-      </c>
-      <c r="I5" t="n">
-        <v>331</v>
-      </c>
-      <c r="J5" t="n">
-        <v>16</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-7.8154</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-78.0467</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>80127 MAYOR SANTIAGO ZAVALA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-7.8177</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-78.0478</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1142</v>
-      </c>
-      <c r="J6" t="n">
-        <v>41</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-7.8177</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-78.0478</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>80128</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-7.81841</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-78.04075</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1915</v>
-      </c>
-      <c r="J7" t="n">
-        <v>67</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-7.81841</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-78.04075</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>80130</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-7.830278</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-78.025785</v>
-      </c>
-      <c r="I8" t="n">
-        <v>214</v>
-      </c>
-      <c r="J8" t="n">
-        <v>13</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-7.830278</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-78.025785</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>80163</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-7.888442</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-78.118668</v>
-      </c>
-      <c r="I9" t="n">
-        <v>267</v>
-      </c>
-      <c r="J9" t="n">
-        <v>26</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-7.888442</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-78.118668</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>80779 LA INMACULADA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-7.811283</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-78.04661900000001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>809</v>
-      </c>
-      <c r="J10" t="n">
-        <v>31</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-7.811283</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-78.046619</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>80872</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-7.8096</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-78.02970000000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>430</v>
-      </c>
-      <c r="J11" t="n">
-        <v>19</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-7.8096</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-78.0297</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>80921 NEMESIO VARGAS MARQUINA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-7.80144</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-78.046933</v>
-      </c>
-      <c r="I12" t="n">
-        <v>660</v>
-      </c>
-      <c r="J12" t="n">
-        <v>26</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-7.80144</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-78.046933</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>SAN NICOLAS</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-7.8159</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-78.0497</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2489</v>
-      </c>
-      <c r="J13" t="n">
-        <v>109</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-7.8159</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-78.0497</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2489</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>81624</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-7.772409</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-78.07238099999999</v>
-      </c>
-      <c r="I14" t="n">
-        <v>226</v>
-      </c>
-      <c r="J14" t="n">
-        <v>17</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-7.772409</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-78.072381</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>82001 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-7.767579</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-77.95460199999999</v>
-      </c>
-      <c r="I15" t="n">
-        <v>201</v>
-      </c>
-      <c r="J15" t="n">
-        <v>18</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-7.767579</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-77.954602</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>FLORENCIA DE MORA</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-7.8171</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-78.0406</v>
-      </c>
-      <c r="I16" t="n">
-        <v>865</v>
-      </c>
-      <c r="J16" t="n">
-        <v>50</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-7.8171</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-78.0406</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>ADVENTISTA</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-7.81136</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-78.04984</v>
-      </c>
-      <c r="I17" t="n">
-        <v>325</v>
-      </c>
-      <c r="J17" t="n">
-        <v>20</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-7.81136</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-78.04984</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>SANTA ANA - SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-7.80856</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-78.05067</v>
-      </c>
-      <c r="I18" t="n">
-        <v>682</v>
-      </c>
-      <c r="J18" t="n">
-        <v>28</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-7.80856</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-78.05067</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>80971</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-7.68072</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-77.811069</v>
-      </c>
-      <c r="I19" t="n">
-        <v>234</v>
-      </c>
-      <c r="J19" t="n">
-        <v>16</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-7.68072</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-77.811069</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>80190 SANTA ROSA</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-7.875588</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-77.667885</v>
-      </c>
-      <c r="I20" t="n">
-        <v>343</v>
-      </c>
-      <c r="J20" t="n">
-        <v>18</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-7.875588</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-77.667885</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>80183</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-7.755441</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-77.90656799999999</v>
-      </c>
-      <c r="I21" t="n">
-        <v>233</v>
-      </c>
-      <c r="J21" t="n">
-        <v>20</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-7.755441</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-77.906568</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>80646</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-7.730699</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-77.906362</v>
-      </c>
-      <c r="I22" t="n">
-        <v>206</v>
-      </c>
-      <c r="J22" t="n">
-        <v>17</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-7.730699</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-77.906362</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>80203</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-7.818566</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-78.15971500000001</v>
-      </c>
-      <c r="I23" t="n">
-        <v>283</v>
-      </c>
-      <c r="J23" t="n">
-        <v>17</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-7.818566</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-78.159715</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>80210 AUGUSTO CESAR SALAZAR BONDY</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-7.779982</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-78.231407</v>
-      </c>
-      <c r="I24" t="n">
-        <v>226</v>
-      </c>
-      <c r="J24" t="n">
-        <v>16</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-7.779982</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-78.231407</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>80214 ANTONIO JOSE BRACK EGG</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-7.934638</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-77.943775</v>
-      </c>
-      <c r="I25" t="n">
-        <v>266</v>
-      </c>
-      <c r="J25" t="n">
-        <v>21</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-7.934638</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-77.943775</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>80218</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-7.968981</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-77.778638</v>
-      </c>
-      <c r="I26" t="n">
-        <v>212</v>
-      </c>
-      <c r="J26" t="n">
-        <v>18</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-7.968981</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-77.778638</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>80148 CIRO ALEGRIA</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-7.699177</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-77.7437</v>
-      </c>
-      <c r="I27" t="n">
-        <v>536</v>
-      </c>
-      <c r="J27" t="n">
-        <v>25</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-7.699177</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-77.7437</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>80731</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-7.592444</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-77.75706599999999</v>
-      </c>
-      <c r="I28" t="n">
-        <v>200</v>
-      </c>
-      <c r="J28" t="n">
-        <v>17</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-7.592444</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-77.757066</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>80152</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-7.7575</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-78.01611</v>
-      </c>
-      <c r="I29" t="n">
-        <v>276</v>
-      </c>
-      <c r="J29" t="n">
-        <v>20</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-7.7575</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-78.01611</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>80779 LA INMACULADA</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-7.813337</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-78.044661</v>
-      </c>
-      <c r="I30" t="n">
-        <v>836</v>
-      </c>
-      <c r="J30" t="n">
-        <v>39</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-7.813337</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-78.044661</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>LIBERTAD</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-7.81792</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-78.04224000000001</v>
-      </c>
-      <c r="I31" t="n">
-        <v>323</v>
-      </c>
-      <c r="J31" t="n">
-        <v>20</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-7.81792</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-78.04224</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>80150 JOSE ABELARDO QUIÑONES GONZALES</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-7.61474</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-77.75566000000001</v>
-      </c>
-      <c r="I32" t="n">
-        <v>391</v>
-      </c>
-      <c r="J32" t="n">
-        <v>27</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-7.61474</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-77.75566</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>MARCELINO PAN Y VINO</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-7.81695</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-78.04774999999999</v>
-      </c>
-      <c r="I33" t="n">
-        <v>443</v>
-      </c>
-      <c r="J33" t="n">
-        <v>22</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-7.81695</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-78.04775</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>80860 RICARDO PINILLOS MARTIN</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-7.893049</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-77.687236</v>
-      </c>
-      <c r="I34" t="n">
-        <v>405</v>
-      </c>
-      <c r="J34" t="n">
-        <v>23</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-7.893049</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-77.687236</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>80173</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-7.816569</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-77.937991</v>
-      </c>
-      <c r="I35" t="n">
-        <v>354</v>
-      </c>
-      <c r="J35" t="n">
-        <v>21</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-7.816569</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-77.937991</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>82115 JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-7.817331</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-78.042607</v>
-      </c>
-      <c r="I36" t="n">
-        <v>929</v>
-      </c>
-      <c r="J36" t="n">
-        <v>38</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-7.817331</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-78.042607</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>ALBERTO RUBENS ALTUNA SOLORZANO</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-7.818</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-78.03973000000001</v>
-      </c>
-      <c r="I37" t="n">
-        <v>353</v>
-      </c>
-      <c r="J37" t="n">
-        <v>19</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-7.818</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-78.03973</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>SANTA ANA - SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-7.80819</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-78.05146999999999</v>
-      </c>
-      <c r="I38" t="n">
-        <v>362</v>
-      </c>
-      <c r="J38" t="n">
-        <v>17</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-7.80819</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-78.05147</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>LEONARDO BRUNI / MI NUEVO AMANECER</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-7.81325</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-78.04975</v>
-      </c>
-      <c r="I39" t="n">
-        <v>408</v>
-      </c>
-      <c r="J39" t="n">
-        <v>30</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-7.81325</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-78.04975</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>EL BUEN PASTOR</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-7.81684</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-78.04483999999999</v>
-      </c>
-      <c r="I40" t="n">
-        <v>585</v>
-      </c>
-      <c r="J40" t="n">
-        <v>30</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-7.81684</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-78.04484</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>585</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LA_LIBERTAD-SANCHEZ_CARRION-HUAMACHUCO.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-SANCHEZ_CARRION-HUAMACHUCO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>268447</t>
+          <t>268471</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-7.8123</t>
+          <t>-7.819586</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-78.0453</t>
+          <t>-78.043915</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>225</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>268466</t>
+          <t>268975</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>SAN NICOLAS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-7.8188</t>
+          <t>-7.8159</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-78.0397</t>
+          <t>-78.0497</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>109</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>268471</t>
+          <t>268466</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-7.819586</t>
+          <t>-7.8188</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-78.043915</t>
+          <t>-78.0397</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>267</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>268602</t>
+          <t>268659</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CUNA JARDIN HUAMACHUCO</t>
+          <t>80130</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-7.8154</t>
+          <t>-7.830278</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-78.0467</t>
+          <t>-78.025785</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>268621</t>
+          <t>268602</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>80127 MAYOR SANTIAGO ZAVALA</t>
+          <t>CUNA JARDIN HUAMACHUCO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-7.8177</t>
+          <t>-7.8154</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-78.0478</t>
+          <t>-78.0467</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>331</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>268635</t>
+          <t>269418</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>80128</t>
+          <t>80971</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-7.81841</t>
+          <t>-7.68072</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-78.04075</t>
+          <t>-77.811069</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>234</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>268659</t>
+          <t>270596</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>80130</t>
+          <t>80210 AUGUSTO CESAR SALAZAR BONDY</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-7.830278</t>
+          <t>-7.779982</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-78.025785</t>
+          <t>-78.231407</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>268843</t>
+          <t>268980</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>80163</t>
+          <t>81624</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-7.888442</t>
+          <t>-7.772409</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-78.118668</t>
+          <t>-78.072381</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>268904</t>
+          <t>270271</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>80779 LA INMACULADA</t>
+          <t>80646</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-7.811283</t>
+          <t>-7.730699</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-78.046619</t>
+          <t>-77.906362</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>206</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>268937</t>
+          <t>270520</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>80872</t>
+          <t>80203</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-7.8096</t>
+          <t>-7.818566</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-78.0297</t>
+          <t>-78.159715</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>283</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>268956</t>
+          <t>271256</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>80921 NEMESIO VARGAS MARQUINA</t>
+          <t>80731</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-7.80144</t>
+          <t>-7.592444</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-78.046933</t>
+          <t>-77.757066</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>268975</t>
+          <t>841228</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SAN NICOLAS</t>
+          <t>SANTA ANA - SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-7.8159</t>
+          <t>-7.80819</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-78.0497</t>
+          <t>-78.05147</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2489</t>
+          <t>362</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>268980</t>
+          <t>269036</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>81624</t>
+          <t>82001 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-7.772409</t>
+          <t>-7.767579</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-78.072381</t>
+          <t>-77.954602</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>201</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,27 +1307,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>269036</t>
+          <t>269734</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>82001 SAN FRANCISCO DE ASIS</t>
+          <t>80190 SANTA ROSA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-7.767579</t>
+          <t>-7.875588</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.954602</t>
+          <t>-77.667885</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>343</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1369,37 +1369,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>269079</t>
+          <t>270898</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FLORENCIA DE MORA</t>
+          <t>80218</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-7.8171</t>
+          <t>-7.968981</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-78.0406</t>
+          <t>-77.778638</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>212</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,37 +1431,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>269140</t>
+          <t>268937</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ADVENTISTA</t>
+          <t>80872</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-7.81136</t>
+          <t>-7.8096</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-78.04984</t>
+          <t>-78.0297</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>430</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>269164</t>
+          <t>786420</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SANTA ANA - SAN FRANCISCO DE ASIS</t>
+          <t>ALBERTO RUBENS ALTUNA SOLORZANO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-7.80856</t>
+          <t>-7.818</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-78.05067</t>
+          <t>-78.03973</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>353</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>269418</t>
+          <t>269140</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>80971</t>
+          <t>ADVENTISTA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-7.68072</t>
+          <t>-7.81136</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.811069</t>
+          <t>-78.04984</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>325</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>269734</t>
+          <t>270172</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>80190 SANTA ROSA</t>
+          <t>80183</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-7.875588</t>
+          <t>-7.755441</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.667885</t>
+          <t>-77.906568</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,27 +1679,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>270172</t>
+          <t>363977</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>80183</t>
+          <t>80152</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-7.755441</t>
+          <t>-7.7575</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.906568</t>
+          <t>-78.01611</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>276</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1741,37 +1741,37 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>270271</t>
+          <t>631193</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>80646</t>
+          <t>LIBERTAD</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-7.730699</t>
+          <t>-7.81792</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.906362</t>
+          <t>-78.04224</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>323</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>270520</t>
+          <t>268447</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>80203</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-7.818566</t>
+          <t>-7.8123</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-78.159715</t>
+          <t>-78.0453</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>617</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>270596</t>
+          <t>270855</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>80210 AUGUSTO CESAR SALAZAR BONDY</t>
+          <t>80214 ANTONIO JOSE BRACK EGG</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-7.779982</t>
+          <t>-7.934638</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-78.231407</t>
+          <t>-77.943775</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>266</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>270855</t>
+          <t>669609</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>80214 ANTONIO JOSE BRACK EGG</t>
+          <t>80173</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-7.934638</t>
+          <t>-7.816569</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.943775</t>
+          <t>-77.937991</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>354</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>270898</t>
+          <t>669483</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>80218</t>
+          <t>MARCELINO PAN Y VINO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-7.968981</t>
+          <t>-7.81695</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.778638</t>
+          <t>-78.04775</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>443</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>271143</t>
+          <t>669548</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>80148 CIRO ALEGRIA</t>
+          <t>80860 RICARDO PINILLOS MARTIN</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-7.699177</t>
+          <t>-7.893049</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.7437</t>
+          <t>-77.687236</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>405</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>271256</t>
+          <t>271143</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>80731</t>
+          <t>80148 CIRO ALEGRIA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-7.592444</t>
+          <t>-7.699177</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.757066</t>
+          <t>-77.7437</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>536</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>363977</t>
+          <t>268843</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>80152</t>
+          <t>80163</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-7.7575</t>
+          <t>-7.888442</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-78.01611</t>
+          <t>-78.118668</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>267</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>580730</t>
+          <t>268956</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>80779 LA INMACULADA</t>
+          <t>80921 NEMESIO VARGAS MARQUINA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-7.813337</t>
+          <t>-7.80144</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-78.044661</t>
+          <t>-78.046933</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>660</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,37 +2299,37 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>631193</t>
+          <t>669402</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>LIBERTAD</t>
+          <t>80150 JOSE ABELARDO QUIÑONES GONZALES</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-7.81792</t>
+          <t>-7.61474</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-78.04224</t>
+          <t>-77.75566</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>391</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>669402</t>
+          <t>269164</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>80150 JOSE ABELARDO QUIÑONES GONZALES</t>
+          <t>SANTA ANA - SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-7.61474</t>
+          <t>-7.80856</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.75566</t>
+          <t>-78.05067</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>682</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>669483</t>
+          <t>849045</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MARCELINO PAN Y VINO</t>
+          <t>LEONARDO BRUNI / MI NUEVO AMANECER</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-7.81695</t>
+          <t>-7.81325</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-78.04775</t>
+          <t>-78.04975</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>408</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>669548</t>
+          <t>850468</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>80860 RICARDO PINILLOS MARTIN</t>
+          <t>EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-7.893049</t>
+          <t>-7.81684</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.687236</t>
+          <t>-78.04484</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>585</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>669609</t>
+          <t>268904</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>80173</t>
+          <t>80779 LA INMACULADA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-7.816569</t>
+          <t>-7.811283</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.937991</t>
+          <t>-78.046619</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>809</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>786420</t>
+          <t>580730</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ALBERTO RUBENS ALTUNA SOLORZANO</t>
+          <t>80779 LA INMACULADA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-7.818</t>
+          <t>-7.813337</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-78.03973</t>
+          <t>-78.044661</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>836</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>841228</t>
+          <t>268621</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SANTA ANA - SAN FRANCISCO DE ASIS</t>
+          <t>80127 MAYOR SANTIAGO ZAVALA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-7.80819</t>
+          <t>-7.8177</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-78.05147</t>
+          <t>-78.0478</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,37 +2795,37 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>849045</t>
+          <t>269079</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>LEONARDO BRUNI / MI NUEVO AMANECER</t>
+          <t>FLORENCIA DE MORA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-7.81325</t>
+          <t>-7.8171</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-78.04975</t>
+          <t>-78.0406</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>865</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>850468</t>
+          <t>268635</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>EL BUEN PASTOR</t>
+          <t>80128</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-7.81684</t>
+          <t>-7.81841</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-78.04484</t>
+          <t>-78.04075</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>67</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">

--- a/ZonasEscolares/excels/LA_LIBERTAD-SANCHEZ_CARRION-HUAMACHUCO.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-SANCHEZ_CARRION-HUAMACHUCO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>268471</t>
+          <t>850468</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-7.819586</t>
+          <t>585</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-78.043915</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>-7.81684</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-78.04484</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>268975</t>
+          <t>849045</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SAN NICOLAS</t>
+          <t>LEONARDO BRUNI / MI NUEVO AMANECER</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-7.8159</t>
+          <t>408</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-78.0497</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2489</t>
+          <t>-7.81325</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>-78.04975</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>268466</t>
+          <t>841228</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>SANTA ANA - SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-7.8188</t>
+          <t>362</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-78.0397</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>-7.80819</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-78.05147</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>268659</t>
+          <t>786420</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>80130</t>
+          <t>ALBERTO RUBENS ALTUNA SOLORZANO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-7.830278</t>
+          <t>353</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-78.025785</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>-7.818</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-78.03973</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>268602</t>
+          <t>755517</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CUNA JARDIN HUAMACHUCO</t>
+          <t>82115 JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-7.8154</t>
+          <t>929</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-78.0467</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>-7.817331</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-78.042607</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>269418</t>
+          <t>669609</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>80971</t>
+          <t>80173</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-7.68072</t>
+          <t>354</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.811069</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>-7.816569</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.937991</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>270596</t>
+          <t>669548</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>80210 AUGUSTO CESAR SALAZAR BONDY</t>
+          <t>80860 RICARDO PINILLOS MARTIN</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-7.779982</t>
+          <t>405</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-78.231407</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>-7.893049</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.687236</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>268980</t>
+          <t>669483</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>81624</t>
+          <t>MARCELINO PAN Y VINO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-7.772409</t>
+          <t>443</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-78.072381</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>-7.81695</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-78.04775</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>270271</t>
+          <t>669402</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>80646</t>
+          <t>80150 JOSE ABELARDO QUIÑONES GONZALES</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-7.730699</t>
+          <t>391</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.906362</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>-7.61474</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.75566</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>270520</t>
+          <t>631193</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>80203</t>
+          <t>LIBERTAD</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-7.818566</t>
+          <t>323</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-78.159715</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>-7.81792</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-78.04224</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>271256</t>
+          <t>580730</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>80731</t>
+          <t>80779 LA INMACULADA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-7.592444</t>
+          <t>836</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.757066</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-7.813337</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-78.044661</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>841228</t>
+          <t>363977</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SANTA ANA - SAN FRANCISCO DE ASIS</t>
+          <t>80152</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-7.80819</t>
+          <t>276</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-78.05147</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>-7.7575</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-78.01611</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>269036</t>
+          <t>271256</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>82001 SAN FRANCISCO DE ASIS</t>
+          <t>80731</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-7.767579</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.954602</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>-7.592444</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.757066</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>269734</t>
+          <t>271143</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>80190 SANTA ROSA</t>
+          <t>80148 CIRO ALEGRIA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-7.875588</t>
+          <t>536</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.667885</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>-7.699177</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.7437</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1379,22 +1379,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>-7.968981</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>-77.778638</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,37 +1431,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>268937</t>
+          <t>270855</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>80872</t>
+          <t>80214 ANTONIO JOSE BRACK EGG</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-7.8096</t>
+          <t>266</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-78.0297</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>-7.934638</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.943775</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>786420</t>
+          <t>270596</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ALBERTO RUBENS ALTUNA SOLORZANO</t>
+          <t>80210 AUGUSTO CESAR SALAZAR BONDY</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-7.818</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-78.03973</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>-7.779982</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-78.231407</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>269140</t>
+          <t>270520</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ADVENTISTA</t>
+          <t>80203</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-7.81136</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-78.04984</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>-7.818566</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-78.159715</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>270172</t>
+          <t>270271</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>80183</t>
+          <t>80646</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-7.755441</t>
+          <t>206</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.906568</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>-7.730699</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.906362</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>363977</t>
+          <t>270172</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>80152</t>
+          <t>80183</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-7.7575</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-78.01611</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>-7.755441</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.906568</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,37 +1741,37 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>631193</t>
+          <t>269734</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>LIBERTAD</t>
+          <t>80190 SANTA ROSA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-7.81792</t>
+          <t>343</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-78.04224</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>-7.875588</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.667885</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>268447</t>
+          <t>269418</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>80971</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-7.8123</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-78.0453</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>-7.68072</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.811069</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>270855</t>
+          <t>269164</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>80214 ANTONIO JOSE BRACK EGG</t>
+          <t>SANTA ANA - SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-7.934638</t>
+          <t>682</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.943775</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>-7.80856</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-78.05067</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>669609</t>
+          <t>269140</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>80173</t>
+          <t>ADVENTISTA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-7.816569</t>
+          <t>325</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.937991</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>-7.81136</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-78.04984</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,37 +1989,37 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>669483</t>
+          <t>269079</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MARCELINO PAN Y VINO</t>
+          <t>FLORENCIA DE MORA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-7.81695</t>
+          <t>865</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-78.04775</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>-7.8171</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-78.0406</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>669548</t>
+          <t>269036</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>80860 RICARDO PINILLOS MARTIN</t>
+          <t>82001 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-7.893049</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.687236</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>-7.767579</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.954602</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>271143</t>
+          <t>268980</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>80148 CIRO ALEGRIA</t>
+          <t>81624</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-7.699177</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.7437</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>-7.772409</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-78.072381</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>268843</t>
+          <t>268975</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>80163</t>
+          <t>SAN NICOLAS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-7.888442</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-78.118668</t>
+          <t>109</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>-7.8159</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-78.0497</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2247,22 +2247,22 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
           <t>-7.80144</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>-78.046933</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>660</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,37 +2299,37 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>669402</t>
+          <t>268937</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>80150 JOSE ABELARDO QUIÑONES GONZALES</t>
+          <t>80872</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-7.61474</t>
+          <t>430</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.75566</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>-7.8096</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-78.0297</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>269164</t>
+          <t>268904</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SANTA ANA - SAN FRANCISCO DE ASIS</t>
+          <t>80779 LA INMACULADA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-7.80856</t>
+          <t>809</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-78.05067</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>-7.811283</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-78.046619</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>849045</t>
+          <t>268843</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>LEONARDO BRUNI / MI NUEVO AMANECER</t>
+          <t>80163</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-7.81325</t>
+          <t>267</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-78.04975</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>-7.888442</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-78.118668</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>850468</t>
+          <t>268659</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>EL BUEN PASTOR</t>
+          <t>80130</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-7.81684</t>
+          <t>214</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-78.04484</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>-7.830278</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-78.025785</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>268904</t>
+          <t>268635</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>80779 LA INMACULADA</t>
+          <t>80128</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-7.811283</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-78.046619</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>-7.81841</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-78.04075</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>755517</t>
+          <t>268621</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>82115 JOSE FAUSTINO SANCHEZ CARRION</t>
+          <t>80127 MAYOR SANTIAGO ZAVALA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-7.817331</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-78.042607</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>-7.8177</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-78.0478</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>580730</t>
+          <t>268602</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>80779 LA INMACULADA</t>
+          <t>CUNA JARDIN HUAMACHUCO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-7.813337</t>
+          <t>331</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-78.044661</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>-7.8154</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-78.0467</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>268621</t>
+          <t>268471</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>80127 MAYOR SANTIAGO ZAVALA</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-7.8177</t>
+          <t>225</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-78.0478</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>-7.819586</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-78.043915</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,37 +2795,37 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>269079</t>
+          <t>268466</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FLORENCIA DE MORA</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-7.8171</t>
+          <t>267</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-78.0406</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>-7.8188</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-78.0397</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>268635</t>
+          <t>268447</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>80128</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-7.81841</t>
+          <t>617</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-78.04075</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>-7.8123</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>-78.0453</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">

--- a/ZonasEscolares/excels/LA_LIBERTAD-SANCHEZ_CARRION-HUAMACHUCO.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-SANCHEZ_CARRION-HUAMACHUCO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
